--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>סתיו שמש – היופי שבאמצע⁩</v>
+        <v>אור קודאי – פירורים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-29</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a1%d7%aa%d7%99%d7%95-%d7%a9%d7%9e%d7%a9-%d7%94%d7%99%d7%95%d7%a4%d7%99-%d7%a9%d7%91%d7%90%d7%9e%d7%a6%d7%a2%e2%81%a9/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a7%d7%95%d7%93%d7%90%d7%99-%d7%a4%d7%99%d7%a8%d7%95%d7%a8%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-29</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"היופי שבאמצע” של סתיו שמש הוא שיר שמנסה לתאר מצב נפשי מאוד עכשווי: חיים בתוך געגוע מתמשך  לא רק לאדם אחר, אלא לגרסאות קודמות של עצמנו, שיר על זיכרון רגשי, על פצע שלא נעלם אלא מחליף צורה, ועל הניסיון ללמוד</v>
+        <v>אור קודאי שר בלדה מלנכולית שנשענת פחות על עלילה ויותר על תחושה – תחושת ריקנות אחרי אהבה שנשחקה עד שלא נותר ממנה כמעט דבר. הדימוי "פירורים" מבטא לא שברון לב דרמטי, אלא שאריות. של משהו שהיה פעם שלם, חם ומזין,</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>סתיו שמש – היופי שבאמצע⁩</v>
+        <v>אור קודאי – פירורים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אור קודאי – פירורים</v>
+        <v>איתי עברון – בא מלמטה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a7%d7%95%d7%93%d7%90%d7%99-%d7%a4%d7%99%d7%a8%d7%95%d7%a8%d7%99%d7%9d/</v>
+        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%a2%d7%91%d7%a8%d7%95%d7%9f-%d7%91%d7%90-%d7%9e%d7%9c%d7%9e%d7%98%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-29</v>
+        <v>2026-05-30</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אור קודאי שר בלדה מלנכולית שנשענת פחות על עלילה ויותר על תחושה – תחושת ריקנות אחרי אהבה שנשחקה עד שלא נותר ממנה כמעט דבר. הדימוי "פירורים" מבטא לא שברון לב דרמטי, אלא שאריות. של משהו שהיה פעם שלם, חם ומזין,</v>
+        <v>"בא מלמטה" של איתי עברון  הוא שיר רוק קברטי-תיאטרלי שמציג דיוקן עצמי חסר מעצורים של אמן צעיר הנאבק בין הצורך להתקבל לבין הדחף להיות נאמן לאש הפנימית שלו. זהו שיר על זהות, מעמד, שאפתנות ועל הסירוב להתנצל על מי שאתה.</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אור קודאי – פירורים</v>
+        <v>איתי עברון – בא מלמטה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L8"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>איתי עברון – בא מלמטה</v>
+        <v>גל חייק - מכתב פרידה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%99%d7%aa%d7%99-%d7%a2%d7%91%d7%a8%d7%95%d7%9f-%d7%91%d7%90-%d7%9e%d7%9c%d7%9e%d7%98%d7%94/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411119&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-30</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>"בא מלמטה" של איתי עברון  הוא שיר רוק קברטי-תיאטרלי שמציג דיוקן עצמי חסר מעצורים של אמן צעיר הנאבק בין הצורך להתקבל לבין הדחף להיות נאמן לאש הפנימית שלו. זהו שיר על זהות, מעמד, שאפתנות ועל הסירוב להתנצל על מי שאתה.</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,240 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>איתי עברון – בא מלמטה</v>
+        <v>גל חייק - מכתב פרידה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>בן-אל - פתאום נעלמת</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411117&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>בן-אל - פתאום נעלמת</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>אמיתי צדוק - כיוון אחד</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411116&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>אמיתי צדוק - כיוון אחד</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411115&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>אלחי מידני - שכחתי לחייך</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411114&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>אלחי מידני - שכחתי לחייך</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>איתי כהן - אל תדאגי לי</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411113&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>איתי כהן - אל תדאגי לי</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411112&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-30</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>גל חייק - מכתב פרידה</v>
+        <v>עידו כנפי - לחזור למוטב</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411119&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411126&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-30</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>גל חייק - מכתב פרידה</v>
+        <v>עידו כנפי - לחזור למוטב</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>בן-אל - פתאום נעלמת</v>
+        <v>מענדי וויס - להודות</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411117&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411125&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-30</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>בן-אל - פתאום נעלמת</v>
+        <v>מענדי וויס - להודות</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>אמיתי צדוק - כיוון אחד</v>
+        <v>מלכה בי - פרא אדם</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411116&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411124&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-30</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>אמיתי צדוק - כיוון אחד</v>
+        <v>מלכה בי - פרא אדם</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
+        <v>ישי סיידוף - הרי הקסטל</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411115&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411123&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-30</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>אלחנן אלחדד &amp; קובי ברומר - אנעים זמירות</v>
+        <v>ישי סיידוף - הרי הקסטל</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>אלחי מידני - שכחתי לחייך</v>
+        <v>יוסף חיים בוסקילה - אשא עיניי</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411114&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411122&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-30</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>אלחי מידני - שכחתי לחייך</v>
+        <v>יוסף חיים בוסקילה - אשא עיניי</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>איתי כהן - אל תדאגי לי</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411113&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411121&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-30</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>איתי כהן - אל תדאגי לי</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-30</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411112&amp;sid=3244ccdeff38871b21c67061ec8dffaf</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411120&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-30</v>
@@ -697,7 +697,7 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>Kaan Ates - Sen Ve Ben (Bedal)</v>
+        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L8"/>
+  <dimension ref="A1:L2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>עידו כנפי - לחזור למוטב</v>
+        <v>ארקדי דוכין – תנו לבלון לעוף</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411126&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
+        <v>https://yosmusic.com/%d7%90%d7%a8%d7%a7%d7%93%d7%99-%d7%93%d7%95%d7%9b%d7%99%d7%9f-%d7%aa%d7%a0%d7%95-%d7%9c%d7%91%d7%9c%d7%95%d7%9f-%d7%9c%d7%a2%d7%95%d7%a3/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-05-30</v>
+        <v>2026-05-31</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v/>
+        <v>הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי דוכין לא הצליח להשתחרר ממנו: השיר נכתב בעקבות הרצח המטלטל של ימנו (בנימין) זלקה ז״ל. אבל זה לא שיר על הרצח. זה שיר על טוב לב. הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,240 +469,12 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>עידו כנפי - לחזור למוטב</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>מענדי וויס - להודות</v>
-      </c>
-      <c r="B3" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411125&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
-      </c>
-      <c r="D3" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E3" t="str">
-        <v/>
-      </c>
-      <c r="F3" t="str">
-        <v/>
-      </c>
-      <c r="G3" t="str">
-        <v/>
-      </c>
-      <c r="H3" t="str">
-        <v/>
-      </c>
-      <c r="I3" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J3" t="str">
-        <v/>
-      </c>
-      <c r="K3" t="str">
-        <v/>
-      </c>
-      <c r="L3" t="str">
-        <v>מענדי וויס - להודות</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="str">
-        <v>מלכה בי - פרא אדם</v>
-      </c>
-      <c r="B4" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411124&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
-      </c>
-      <c r="D4" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E4" t="str">
-        <v/>
-      </c>
-      <c r="F4" t="str">
-        <v/>
-      </c>
-      <c r="G4" t="str">
-        <v/>
-      </c>
-      <c r="H4" t="str">
-        <v/>
-      </c>
-      <c r="I4" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J4" t="str">
-        <v/>
-      </c>
-      <c r="K4" t="str">
-        <v/>
-      </c>
-      <c r="L4" t="str">
-        <v>מלכה בי - פרא אדם</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ישי סיידוף - הרי הקסטל</v>
-      </c>
-      <c r="B5" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411123&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
-      </c>
-      <c r="D5" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E5" t="str">
-        <v/>
-      </c>
-      <c r="F5" t="str">
-        <v/>
-      </c>
-      <c r="G5" t="str">
-        <v/>
-      </c>
-      <c r="H5" t="str">
-        <v/>
-      </c>
-      <c r="I5" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-      <c r="K5" t="str">
-        <v/>
-      </c>
-      <c r="L5" t="str">
-        <v>ישי סיידוף - הרי הקסטל</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>יוסף חיים בוסקילה - אשא עיניי</v>
-      </c>
-      <c r="B6" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411122&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
-      </c>
-      <c r="D6" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E6" t="str">
-        <v/>
-      </c>
-      <c r="F6" t="str">
-        <v/>
-      </c>
-      <c r="G6" t="str">
-        <v/>
-      </c>
-      <c r="H6" t="str">
-        <v/>
-      </c>
-      <c r="I6" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-      <c r="K6" t="str">
-        <v/>
-      </c>
-      <c r="L6" t="str">
-        <v>יוסף חיים בוסקילה - אשא עיניי</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
-      </c>
-      <c r="B7" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411121&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
-      </c>
-      <c r="D7" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E7" t="str">
-        <v/>
-      </c>
-      <c r="F7" t="str">
-        <v/>
-      </c>
-      <c r="G7" t="str">
-        <v/>
-      </c>
-      <c r="H7" t="str">
-        <v/>
-      </c>
-      <c r="I7" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J7" t="str">
-        <v/>
-      </c>
-      <c r="K7" t="str">
-        <v/>
-      </c>
-      <c r="L7" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת יוונית 2026</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
-      </c>
-      <c r="B8" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411120&amp;sid=5838eefd5936ee1111d4e0008c7266c1</v>
-      </c>
-      <c r="D8" t="str">
-        <v>2026-05-30</v>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8" t="str">
-        <v/>
-      </c>
-      <c r="G8" t="str">
-        <v/>
-      </c>
-      <c r="H8" t="str">
-        <v/>
-      </c>
-      <c r="I8" t="str">
-        <v>סינגלים חדשים</v>
-      </c>
-      <c r="J8" t="str">
-        <v/>
-      </c>
-      <c r="K8" t="str">
-        <v/>
-      </c>
-      <c r="L8" t="str">
-        <v>היוצרים - מחווה לקלאסיקות - מחרוזת זוהר ארגוב 2026</v>
+        <v>ארקדי דוכין – תנו לבלון לעוף</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:L2"/>
+  <dimension ref="A1:L12"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ארקדי דוכין – תנו לבלון לעוף</v>
+        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a8%d7%a7%d7%93%d7%99-%d7%93%d7%95%d7%9b%d7%99%d7%9f-%d7%aa%d7%a0%d7%95-%d7%9c%d7%91%d7%9c%d7%95%d7%9f-%d7%9c%d7%a2%d7%95%d7%a3/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411136&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-31</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי דוכין לא הצליח להשתחרר ממנו: השיר נכתב בעקבות הרצח המטלטל של ימנו (בנימין) זלקה ז״ל. אבל זה לא שיר על הרצח. זה שיר על טוב לב. הטריגר לכתיבה היה סיפור קטן ואמיתי שארקדי</v>
+        <v/>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,12 +469,392 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ארקדי דוכין – תנו לבלון לעוף</v>
+        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>שחר כהן - מיי לייף</v>
+      </c>
+      <c r="B3" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C3" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411135&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D3" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
+        <v/>
+      </c>
+      <c r="H3" t="str">
+        <v/>
+      </c>
+      <c r="I3" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J3" t="str">
+        <v/>
+      </c>
+      <c r="K3" t="str">
+        <v/>
+      </c>
+      <c r="L3" t="str">
+        <v>שחר כהן - מיי לייף</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>שון שחר - סקסי גירל</v>
+      </c>
+      <c r="B4" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C4" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411134&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D4" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E4" t="str">
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J4" t="str">
+        <v/>
+      </c>
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v>שון שחר - סקסי גירל</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ענבל רז - לא כותבת על אקסים</v>
+      </c>
+      <c r="B5" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C5" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411133&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D5" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E5" t="str">
+        <v/>
+      </c>
+      <c r="F5" t="str">
+        <v/>
+      </c>
+      <c r="G5" t="str">
+        <v/>
+      </c>
+      <c r="H5" t="str">
+        <v/>
+      </c>
+      <c r="I5" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J5" t="str">
+        <v/>
+      </c>
+      <c r="K5" t="str">
+        <v/>
+      </c>
+      <c r="L5" t="str">
+        <v>ענבל רז - לא כותבת על אקסים</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="str">
+        <v>סאלי - מה ששלי שלי</v>
+      </c>
+      <c r="B6" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C6" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411132&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D6" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E6" t="str">
+        <v/>
+      </c>
+      <c r="F6" t="str">
+        <v/>
+      </c>
+      <c r="G6" t="str">
+        <v/>
+      </c>
+      <c r="H6" t="str">
+        <v/>
+      </c>
+      <c r="I6" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J6" t="str">
+        <v/>
+      </c>
+      <c r="K6" t="str">
+        <v/>
+      </c>
+      <c r="L6" t="str">
+        <v>סאלי - מה ששלי שלי</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>חיים איפרגן - יום חדש</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C7" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411131&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D7" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E7" t="str">
+        <v/>
+      </c>
+      <c r="F7" t="str">
+        <v/>
+      </c>
+      <c r="G7" t="str">
+        <v/>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+      <c r="I7" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J7" t="str">
+        <v/>
+      </c>
+      <c r="K7" t="str">
+        <v/>
+      </c>
+      <c r="L7" t="str">
+        <v>חיים איפרגן - יום חדש</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C8" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411130&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D8" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E8" t="str">
+        <v/>
+      </c>
+      <c r="F8" t="str">
+        <v/>
+      </c>
+      <c r="G8" t="str">
+        <v/>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+      <c r="I8" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J8" t="str">
+        <v/>
+      </c>
+      <c r="K8" t="str">
+        <v/>
+      </c>
+      <c r="L8" t="str">
+        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>אסאלה - חיים שלי בלב</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C9" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411129&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D9" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E9" t="str">
+        <v/>
+      </c>
+      <c r="F9" t="str">
+        <v/>
+      </c>
+      <c r="G9" t="str">
+        <v/>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+      <c r="I9" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J9" t="str">
+        <v/>
+      </c>
+      <c r="K9" t="str">
+        <v/>
+      </c>
+      <c r="L9" t="str">
+        <v>אסאלה - חיים שלי בלב</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>אילנה עדני - מאיר לי אותי</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C10" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411128&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D10" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E10" t="str">
+        <v/>
+      </c>
+      <c r="F10" t="str">
+        <v/>
+      </c>
+      <c r="G10" t="str">
+        <v/>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+      <c r="I10" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J10" t="str">
+        <v/>
+      </c>
+      <c r="K10" t="str">
+        <v/>
+      </c>
+      <c r="L10" t="str">
+        <v>אילנה עדני - מאיר לי אותי</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C11" t="str">
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411127&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+      </c>
+      <c r="D11" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E11" t="str">
+        <v/>
+      </c>
+      <c r="F11" t="str">
+        <v/>
+      </c>
+      <c r="G11" t="str">
+        <v/>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+      <c r="I11" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J11" t="str">
+        <v/>
+      </c>
+      <c r="K11" t="str">
+        <v/>
+      </c>
+      <c r="L11" t="str">
+        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>יובל דיין – לא להרגיש כלל</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="C12" t="str">
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%93%d7%99%d7%99%d7%9f-%d7%9c%d7%90-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%9b%d7%9c%d7%9c/</v>
+      </c>
+      <c r="D12" t="str">
+        <v>2026-05-31</v>
+      </c>
+      <c r="E12" t="str">
+        <v/>
+      </c>
+      <c r="F12" t="str">
+        <v>"לא להרגיש כלל" הוא שיר שעוסק במנגנוני הימנעות רגשיים – הרצון לברוח מכאב, חרדה ועצב במקום להתמודד איתם. מה שמעניין בו הוא שהמילים והמוזיקה פועלות בכיוונים משלימים: הטקסט מתאר הכחשה ובריחה, בעוד שהלחן והביצוע של יובל דיין מעניקים לשיר תחושה</v>
+      </c>
+      <c r="G12" t="str">
+        <v/>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+      <c r="I12" t="str">
+        <v>סינגלים חדשים</v>
+      </c>
+      <c r="J12" t="str">
+        <v/>
+      </c>
+      <c r="K12" t="str">
+        <v/>
+      </c>
+      <c r="L12" t="str">
+        <v>יובל דיין – לא להרגיש כלל</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:L2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:L12"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
+++ b/data/tags/סינגלים חדשים/global/2026-05-week05/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
+        <v>ליאם שמואל - דוז פואה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C2" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411136&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411147&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D2" t="str">
         <v>2026-05-31</v>
@@ -469,18 +469,18 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>שלומי שבת &amp; עמיר בניון - היכן אתה</v>
+        <v>ליאם שמואל - דוז פואה</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>שחר כהן - מיי לייף</v>
+        <v>וואן דאן - באדמאן</v>
       </c>
       <c r="B3" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C3" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411135&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411146&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D3" t="str">
         <v>2026-05-31</v>
@@ -507,18 +507,18 @@
         <v/>
       </c>
       <c r="L3" t="str">
-        <v>שחר כהן - מיי לייף</v>
+        <v>וואן דאן - באדמאן</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>שון שחר - סקסי גירל</v>
+        <v>גיא קהלני - פאזל</v>
       </c>
       <c r="B4" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C4" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411134&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411145&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D4" t="str">
         <v>2026-05-31</v>
@@ -545,18 +545,18 @@
         <v/>
       </c>
       <c r="L4" t="str">
-        <v>שון שחר - סקסי גירל</v>
+        <v>גיא קהלני - פאזל</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>ענבל רז - לא כותבת על אקסים</v>
+        <v>שיר גבאי - תרקדי</v>
       </c>
       <c r="B5" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C5" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411133&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411144&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D5" t="str">
         <v>2026-05-31</v>
@@ -583,18 +583,18 @@
         <v/>
       </c>
       <c r="L5" t="str">
-        <v>ענבל רז - לא כותבת על אקסים</v>
+        <v>שיר גבאי - תרקדי</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="str">
-        <v>סאלי - מה ששלי שלי</v>
+        <v>עדן מאירי - טוב מושך אליו טוב</v>
       </c>
       <c r="B6" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C6" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411132&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411143&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D6" t="str">
         <v>2026-05-31</v>
@@ -621,18 +621,18 @@
         <v/>
       </c>
       <c r="L6" t="str">
-        <v>סאלי - מה ששלי שלי</v>
+        <v>עדן מאירי - טוב מושך אליו טוב</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>חיים איפרגן - יום חדש</v>
+        <v>מאיה דדון - ילדה מהפריפריה</v>
       </c>
       <c r="B7" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C7" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411131&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411142&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D7" t="str">
         <v>2026-05-31</v>
@@ -659,18 +659,18 @@
         <v/>
       </c>
       <c r="L7" t="str">
-        <v>חיים איפרגן - יום חדש</v>
+        <v>מאיה דדון - ילדה מהפריפריה</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+        <v>יובל דיין - לא להרגיש כלל</v>
       </c>
       <c r="B8" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C8" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411130&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411141&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D8" t="str">
         <v>2026-05-31</v>
@@ -697,18 +697,18 @@
         <v/>
       </c>
       <c r="L8" t="str">
-        <v>ארקדי דוכין - תנו לבלון לעוף</v>
+        <v>יובל דיין - לא להרגיש כלל</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>אסאלה - חיים שלי בלב</v>
+        <v>גל אוקטן - העיר הזאת</v>
       </c>
       <c r="B9" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C9" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411129&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411140&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D9" t="str">
         <v>2026-05-31</v>
@@ -735,18 +735,18 @@
         <v/>
       </c>
       <c r="L9" t="str">
-        <v>אסאלה - חיים שלי בלב</v>
+        <v>גל אוקטן - העיר הזאת</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v>אילנה עדני - מאיר לי אותי</v>
+        <v>גדי אלטמן &amp; מרב סמן טוב - לאט לאט בשקט</v>
       </c>
       <c r="B10" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C10" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411128&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411139&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D10" t="str">
         <v>2026-05-31</v>
@@ -773,18 +773,18 @@
         <v/>
       </c>
       <c r="L10" t="str">
-        <v>אילנה עדני - מאיר לי אותי</v>
+        <v>גדי אלטמן &amp; מרב סמן טוב - לאט לאט בשקט</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+        <v>איתי לוי - מה שקשה להגיד</v>
       </c>
       <c r="B11" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C11" t="str">
-        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411127&amp;sid=147cbcf03267d000549f32468ee3e41d</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411138&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D11" t="str">
         <v>2026-05-31</v>
@@ -811,18 +811,18 @@
         <v/>
       </c>
       <c r="L11" t="str">
-        <v>אביעד סהר - מחרוזת יוסף 2026</v>
+        <v>איתי לוי - מה שקשה להגיד</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>יובל דיין – לא להרגיש כלל</v>
+        <v>אבישי אזיקרי - לחיי התחלות חדשות</v>
       </c>
       <c r="B12" t="str">
         <v>2026-05-31</v>
       </c>
       <c r="C12" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%93%d7%99%d7%99%d7%9f-%d7%9c%d7%90-%d7%9c%d7%94%d7%a8%d7%92%d7%99%d7%a9-%d7%9b%d7%9c%d7%9c/</v>
+        <v>http://www.mizrahit.co/viewtopic.php?f=44&amp;t=411137&amp;sid=8aba14c06b8eb2f265205377aa866349</v>
       </c>
       <c r="D12" t="str">
         <v>2026-05-31</v>
@@ -831,7 +831,7 @@
         <v/>
       </c>
       <c r="F12" t="str">
-        <v>"לא להרגיש כלל" הוא שיר שעוסק במנגנוני הימנעות רגשיים – הרצון לברוח מכאב, חרדה ועצב במקום להתמודד איתם. מה שמעניין בו הוא שהמילים והמוזיקה פועלות בכיוונים משלימים: הטקסט מתאר הכחשה ובריחה, בעוד שהלחן והביצוע של יובל דיין מעניקים לשיר תחושה</v>
+        <v/>
       </c>
       <c r="G12" t="str">
         <v/>
@@ -849,7 +849,7 @@
         <v/>
       </c>
       <c r="L12" t="str">
-        <v>יובל דיין – לא להרגיש כלל</v>
+        <v>אבישי אזיקרי - לחיי התחלות חדשות</v>
       </c>
     </row>
   </sheetData>
